--- a/.github/workflows/bulkimport 1.xlsx
+++ b/.github/workflows/bulkimport 1.xlsx
@@ -1,25 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
-  <workbookPr defaultThemeVersion="202300"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\navee\Downloads\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B69126DC-50B6-4056-A808-0964CAE162AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="-113" yWindow="-113" windowWidth="24267" windowHeight="13749" xr2:uid="{E7CD6B03-A029-4A02-9418-1FB4962B9453}"/>
+    <workbookView windowWidth="23040" windowHeight="9840"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
@@ -31,35 +22,32 @@
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="2"/>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="16">
-  <si>
-    <t>user_email</t>
-  </si>
-  <si>
-    <t>user_name</t>
-  </si>
-  <si>
-    <t>user_number</t>
-  </si>
-  <si>
-    <t>user_dob</t>
-  </si>
-  <si>
-    <t>user_gender</t>
-  </si>
-  <si>
-    <t>user_city</t>
-  </si>
-  <si>
-    <t>user_state</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="17">
+  <si>
+    <t>Email</t>
+  </si>
+  <si>
+    <t>Name</t>
+  </si>
+  <si>
+    <t>Number</t>
+  </si>
+  <si>
+    <t>DOB</t>
+  </si>
+  <si>
+    <t>Gender</t>
+  </si>
+  <si>
+    <t>City</t>
+  </si>
+  <si>
+    <t>State</t>
   </si>
   <si>
     <t>tester.jin@gmail.com</t>
@@ -87,43 +75,377 @@
   </si>
   <si>
     <t>Mumbai</t>
+  </si>
+  <si>
+    <t>parthasarathyg694@gmail.com</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="5">
+    <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_ &quot;₹&quot;* #,##0.00_ ;_ &quot;₹&quot;* \-#,##0.00_ ;_ &quot;₹&quot;* &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="179" formatCode="_ &quot;₹&quot;* #,##0_ ;_ &quot;₹&quot;* \-#,##0_ ;_ &quot;₹&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="180" formatCode="yyyy/mm/dd\ hh:mm:ss"/>
+  </numFmts>
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <u/>
       <sz val="11"/>
-      <color theme="10"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="Cascadia Mono"/>
-      <family val="3"/>
+      <color rgb="FF0000FF"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -131,29 +453,312 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="180" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="6"/>
   </cellXfs>
-  <cellStyles count="2">
-    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
+  <cellStyles count="49">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Comma" xfId="1" builtinId="3"/>
+    <cellStyle name="Currency" xfId="2" builtinId="4"/>
+    <cellStyle name="Percent" xfId="3" builtinId="5"/>
+    <cellStyle name="Comma [0]" xfId="4" builtinId="6"/>
+    <cellStyle name="Currency [0]" xfId="5" builtinId="7"/>
+    <cellStyle name="Link" xfId="6" builtinId="8"/>
+    <cellStyle name="Followed Hyperlink" xfId="7" builtinId="9"/>
+    <cellStyle name="Note" xfId="8" builtinId="10"/>
+    <cellStyle name="Warning Text" xfId="9" builtinId="11"/>
+    <cellStyle name="Title" xfId="10" builtinId="15"/>
+    <cellStyle name="CExplanatory Text" xfId="11" builtinId="53"/>
+    <cellStyle name="Heading 1" xfId="12" builtinId="16"/>
+    <cellStyle name="Heading 2" xfId="13" builtinId="17"/>
+    <cellStyle name="Heading 3" xfId="14" builtinId="18"/>
+    <cellStyle name="Heading 4" xfId="15" builtinId="19"/>
+    <cellStyle name="Input" xfId="16" builtinId="20"/>
+    <cellStyle name="Output" xfId="17" builtinId="21"/>
+    <cellStyle name="Calculation" xfId="18" builtinId="22"/>
+    <cellStyle name="Check Cell" xfId="19" builtinId="23"/>
+    <cellStyle name="Linked Cell" xfId="20" builtinId="24"/>
+    <cellStyle name="Total" xfId="21" builtinId="25"/>
+    <cellStyle name="Good" xfId="22" builtinId="26"/>
+    <cellStyle name="Bad" xfId="23" builtinId="27"/>
+    <cellStyle name="Neutral" xfId="24" builtinId="28"/>
+    <cellStyle name="Accent1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - Accent1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - Accent1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - Accent1" xfId="28" builtinId="32"/>
+    <cellStyle name="Accent2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - Accent2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - Accent2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - Accent2" xfId="32" builtinId="36"/>
+    <cellStyle name="Accent3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - Accent3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - Accent3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - Accent3" xfId="36" builtinId="40"/>
+    <cellStyle name="Accent4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - Accent4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - Accent4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - Accent4" xfId="40" builtinId="44"/>
+    <cellStyle name="Accent5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - Accent5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - Accent5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - Accent5" xfId="44" builtinId="48"/>
+    <cellStyle name="Accent6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - Accent6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - Accent6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - Accent6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -170,44 +775,44 @@
         <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="0E2841"/>
+        <a:srgbClr val="1F497D"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="E8E8E8"/>
+        <a:srgbClr val="EEECE1"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="156082"/>
+        <a:srgbClr val="4F81BD"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="E97132"/>
+        <a:srgbClr val="C0504D"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="196B24"/>
+        <a:srgbClr val="9BBB59"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="0F9ED5"/>
+        <a:srgbClr val="8064A2"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="A02B93"/>
+        <a:srgbClr val="4BACC6"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="4EA72E"/>
+        <a:srgbClr val="F79646"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="467886"/>
+        <a:srgbClr val="0000FF"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="96607D"/>
+        <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Aptos Display" panose="02110004020202020204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック Light"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线 Light"/>
+        <a:font script="Hans" typeface="宋体"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Times New Roman"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
@@ -234,32 +839,14 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线"/>
+        <a:font script="Hans" typeface="宋体"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Arial"/>
         <a:font script="Hebr" typeface="Arial"/>
@@ -286,24 +873,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -315,181 +884,180 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:lumMod val="110000"/>
-                <a:satMod val="105000"/>
-                <a:tint val="67000"/>
+                <a:tint val="50000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="35000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="103000"/>
-                <a:tint val="73000"/>
+                <a:tint val="37000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="109000"/>
-                <a:tint val="81000"/>
+                <a:tint val="15000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="16200000" scaled="1"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:satMod val="103000"/>
-                <a:lumMod val="102000"/>
-                <a:tint val="94000"/>
+                <a:shade val="51000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="80000">
               <a:schemeClr val="phClr">
-                <a:satMod val="110000"/>
-                <a:lumMod val="100000"/>
-                <a:shade val="100000"/>
+                <a:shade val="93000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="99000"/>
-                <a:satMod val="120000"/>
-                <a:shade val="78000"/>
+                <a:shade val="94000"/>
+                <a:satMod val="135000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="16200000" scaled="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
-            <a:schemeClr val="phClr"/>
+            <a:schemeClr val="phClr">
+              <a:shade val="95000"/>
+              <a:satMod val="105000"/>
+            </a:schemeClr>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
-        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
         <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
-          <a:effectLst/>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst/>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="38000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
-                <a:alpha val="63000"/>
+                <a:alpha val="35000"/>
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+          <a:scene3d>
+            <a:camera prst="orthographicFront">
+              <a:rot lat="0" lon="0" rev="0"/>
+            </a:camera>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
+            </a:lightRig>
+          </a:scene3d>
+          <a:sp3d>
+            <a:bevelT w="63500" h="25400"/>
+          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="phClr">
-            <a:tint val="95000"/>
-            <a:satMod val="170000"/>
-          </a:schemeClr>
-        </a:solidFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="93000"/>
-                <a:satMod val="150000"/>
-                <a:shade val="98000"/>
-                <a:lumMod val="102000"/>
+                <a:tint val="40000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="40000">
               <a:schemeClr val="phClr">
-                <a:tint val="98000"/>
-                <a:satMod val="130000"/>
-                <a:shade val="90000"/>
-                <a:lumMod val="103000"/>
+                <a:tint val="45000"/>
+                <a:shade val="99000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="63000"/>
-                <a:satMod val="120000"/>
+                <a:shade val="20000"/>
+                <a:satMod val="255000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
+          </a:path>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="80000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="30000"/>
+                <a:satMod val="200000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
+          </a:path>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults>
-    <a:lnDef>
-      <a:spPr/>
-      <a:bodyPr/>
-      <a:lstStyle/>
-      <a:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </a:style>
-    </a:lnDef>
-  </a:objectDefaults>
-  <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
-    </a:ext>
-  </a:extLst>
+  <a:objectDefaults/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1B87B321-038B-41FA-8E62-8E4A4669F378}">
-  <dimension ref="A1:G3"/>
-  <sheetFormatPr defaultRowHeight="15.05" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:G4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="3" outlineLevelCol="6"/>
   <cols>
-    <col min="1" max="1" width="22.44140625" customWidth="1"/>
-    <col min="2" max="2" width="14.21875" customWidth="1"/>
-    <col min="3" max="3" width="20.21875" customWidth="1"/>
-    <col min="4" max="4" width="11.77734375" customWidth="1"/>
-    <col min="5" max="5" width="11.21875" customWidth="1"/>
-    <col min="7" max="7" width="12.77734375" customWidth="1"/>
-    <col min="8" max="8" width="11.33203125" customWidth="1"/>
+    <col min="3" max="3" width="11.7777777777778"/>
+    <col min="4" max="4" width="19.6666666666667"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A1" s="3" t="s">
+    <row r="1" spans="1:7">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
@@ -507,12 +1075,12 @@
       <c r="F1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="G1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2" s="1" t="s">
+    <row r="2" spans="1:7">
+      <c r="A2" t="s">
         <v>7</v>
       </c>
       <c r="B2" t="s">
@@ -521,7 +1089,7 @@
       <c r="C2">
         <v>8610903815</v>
       </c>
-      <c r="D2" s="2">
+      <c r="D2" s="1">
         <v>36651</v>
       </c>
       <c r="E2" t="s">
@@ -534,8 +1102,8 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A3" s="1" t="s">
+    <row r="3" spans="1:7">
+      <c r="A3" t="s">
         <v>12</v>
       </c>
       <c r="B3" t="s">
@@ -544,7 +1112,7 @@
       <c r="C3">
         <v>5648792130</v>
       </c>
-      <c r="D3" s="2">
+      <c r="D3" s="1">
         <v>37571</v>
       </c>
       <c r="E3" t="s">
@@ -554,14 +1122,37 @@
         <v>15</v>
       </c>
       <c r="G3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C4">
+        <v>5648792131</v>
+      </c>
+      <c r="D4" s="1">
+        <v>37572</v>
+      </c>
+      <c r="E4" t="s">
+        <v>14</v>
+      </c>
+      <c r="F4" t="s">
+        <v>15</v>
+      </c>
+      <c r="G4" t="s">
         <v>11</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="A2" r:id="rId1" xr:uid="{669F5BAE-0C08-4666-913E-E7D871BC29B9}"/>
-    <hyperlink ref="A3" r:id="rId2" xr:uid="{CE650904-ECA1-48BE-878A-C24D5BC3B076}"/>
+    <hyperlink ref="A4" r:id="rId1" display="parthasarathyg694@gmail.com"/>
   </hyperlinks>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
 </worksheet>
 </file>